--- a/user.xlsx
+++ b/user.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\demo-data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nckh-tdc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{596269CE-2F92-4315-B1DA-760D9F4DA143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BFDD0DC-78FA-48CF-A118-EDADEA474047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5CB35C19-53DB-4FD7-B62D-7A4B604B7D4B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
   <si>
     <t>tk</t>
   </si>
@@ -50,9 +50,6 @@
     <t>role</t>
   </si>
   <si>
-    <t>ADMIN01</t>
-  </si>
-  <si>
     <t>23211TT1111</t>
   </si>
   <si>
@@ -90,9 +87,6 @@
   </si>
   <si>
     <t>TKDH</t>
-  </si>
-  <si>
-    <t>admin</t>
   </si>
   <si>
     <t>student</t>
@@ -185,9 +179,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -528,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2624A848-4CA6-4EE0-BBD5-1B8A412BC6D6}">
-  <dimension ref="D3:G12"/>
+  <dimension ref="D4:G12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="22.88671875" customWidth="1"/>
@@ -536,142 +529,130 @@
     <col min="6" max="6" width="27.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
     <row r="4" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="1">
-        <v>12345678</v>
-      </c>
-      <c r="F4" s="6" t="s">
+      <c r="E5" s="4">
+        <v>12345678</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D6" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="6">
+        <v>12345678</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="3">
+        <v>12345678</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2">
+        <v>12345678</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3">
+        <v>12345678</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="5">
-        <v>12345678</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="5" t="s">
+      <c r="G9" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="4">
+        <v>12345678</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2">
+        <v>12345678</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D6" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="7">
-        <v>12345678</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="4">
-        <v>12345678</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="3">
-        <v>12345678</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="3" t="s">
+    <row r="12" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="6">
+        <v>12345678</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="4">
-        <v>12345678</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D10" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="5">
-        <v>12345678</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="3">
-        <v>12345678</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="7">
-        <v>12345678</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
